--- a/BackEnd/Server/Controllers/FastReport/TaxTemplates/Mau_Phieunhapmua.xlsx
+++ b/BackEnd/Server/Controllers/FastReport/TaxTemplates/Mau_Phieunhapmua.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="19320" windowHeight="12220" activeTab="1"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="19320" windowHeight="12220"/>
   </bookViews>
   <sheets>
     <sheet name="CT" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Số phiếu</t>
   </si>
@@ -55,12 +55,6 @@
     <t>Người giao hàng</t>
   </si>
   <si>
-    <t>NM001</t>
-  </si>
-  <si>
-    <t>NM002</t>
-  </si>
-  <si>
     <t>Ngµy CT</t>
   </si>
   <si>
@@ -94,15 +88,6 @@
     <t>Địa chỉ VAT</t>
   </si>
   <si>
-    <t xml:space="preserve">120150UNAMOURa          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">185240UNARMORa          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">§Çu c¸p co nhiÖt h¹ thÕ GTS-1/4(3+1) C-0.6/1KV 3                                                </t>
-  </si>
-  <si>
     <t>M· hµng</t>
   </si>
   <si>
@@ -116,9 +101,6 @@
   </si>
   <si>
     <t>Kho</t>
-  </si>
-  <si>
-    <t>KHHH</t>
   </si>
 </sst>
 </file>
@@ -541,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="5" customWidth="1"/>
@@ -558,66 +540,26 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="7">
-        <v>10</v>
-      </c>
-      <c r="E2" s="7">
-        <v>20000</v>
-      </c>
-      <c r="F2" s="7">
-        <v>200000</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="7">
-        <v>200</v>
-      </c>
-      <c r="E3" s="7">
-        <v>25000</v>
-      </c>
-      <c r="F3" s="7">
-        <v>5000000</v>
-      </c>
+      <c r="G2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -652,13 +594,13 @@
   <sheetData>
     <row r="1" spans="1:18" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>7</v>
@@ -667,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>3</v>
@@ -679,31 +621,31 @@
         <v>5</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
